--- a/client/public/products/pack4-cpars-playbook/cpars-playbook.xlsx
+++ b/client/public/products/pack4-cpars-playbook/cpars-playbook.xlsx
@@ -23,9 +23,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -160,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -194,7 +193,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -221,7 +220,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,6 +228,13 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1758,7 +1764,7 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="26" t="n">
         <v>46217</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1798,7 +1804,7 @@
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="26" t="n">
         <v>46231</v>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1838,7 +1844,7 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="26" t="n">
         <v>46239</v>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1878,7 +1884,7 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="26" t="n">
         <v>46253</v>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1918,7 +1924,7 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="26" t="n">
         <v>46264</v>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1958,7 +1964,7 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="26" t="n">
         <v>46268</v>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -2870,7 +2876,7 @@
         </is>
       </c>
       <c r="C15" s="18">
-        <f>IF(E6&gt;0,"Marginal or below",IF(D6&gt;=4,"Exceptional",IF(D6&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E6&gt;0,"Marginal or below",IF(D6-F6&gt;=4,"Exceptional",IF(D6-F6&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D15" s="18">
@@ -2889,7 +2895,7 @@
         </is>
       </c>
       <c r="C16" s="18">
-        <f>IF(E7&gt;0,"Marginal or below",IF(D7&gt;=4,"Exceptional",IF(D7&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E7&gt;0,"Marginal or below",IF(D7-F7&gt;=4,"Exceptional",IF(D7-F7&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D16" s="18">
@@ -2908,7 +2914,7 @@
         </is>
       </c>
       <c r="C17" s="18">
-        <f>IF(E8&gt;0,"Marginal or below",IF(D8&gt;=4,"Exceptional",IF(D8&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E8&gt;0,"Marginal or below",IF(D8-F8&gt;=4,"Exceptional",IF(D8-F8&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D17" s="18">
@@ -2927,7 +2933,7 @@
         </is>
       </c>
       <c r="C18" s="18">
-        <f>IF(E9&gt;0,"Marginal or below",IF(D9&gt;=4,"Exceptional",IF(D9&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E9&gt;0,"Marginal or below",IF(D9-F9&gt;=4,"Exceptional",IF(D9-F9&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D18" s="18">
@@ -2946,7 +2952,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>IF(E10&gt;0,"Marginal or below",IF(D10&gt;=4,"Exceptional",IF(D10&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E10&gt;0,"Marginal or below",IF(D10-F10&gt;=4,"Exceptional",IF(D10-F10&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D19" s="18">
@@ -2965,7 +2971,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>IF(E11&gt;0,"Marginal or below",IF(D11&gt;=4,"Exceptional",IF(D11&gt;=2,"Very Good","Satisfactory")))</f>
+        <f>IF(E11&gt;0,"Marginal or below",IF(D11-F11&gt;=4,"Exceptional",IF(D11-F11&gt;=2,"Very Good","Satisfactory")))</f>
         <v/>
       </c>
       <c r="D20" s="18">
@@ -3324,7 +3330,7 @@
           <t>Draft notification date:</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="27" t="n">
         <v>46280</v>
       </c>
     </row>
@@ -3568,8 +3574,8 @@
   <mergeCells count="14">
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="B17:G17"/>

--- a/client/public/products/pack4-cpars-playbook/cpars-playbook.xlsx
+++ b/client/public/products/pack4-cpars-playbook/cpars-playbook.xlsx
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Completed CMMC Level 2 C3PAO assessment two months ahead of the Phase 2 effective date; all subcontractors handling CUI assessed.</t>
+          <t>Posted a current CMMC Level 2 self-assessment in SPRS and closed the last POA&amp;M item 40 days early; confirmed both CUI-handling subcontractors are current.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Program has no CMMC risk at Phase 2 (Nov 10, 2026); Government did not have to track it.</t>
+          <t>CO's SPRS check before the option exercise came back clean; the Government did not have to follow up.</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
